--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ИВОН СТРОЙ 2015 ЕООД" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -67,6 +70,15 @@
     <t>2026-05-08</t>
   </si>
   <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1163 София Ботевградско шосе</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
     <t>ДЛ5</t>
   </si>
   <si>
@@ -76,19 +88,37 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>07:02</t>
-  </si>
-  <si>
-    <t>22:38</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>07:08</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:02:00</t>
+  </si>
+  <si>
+    <t>22:38:00</t>
+  </si>
+  <si>
+    <t>09:15:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>07:07:00</t>
+  </si>
+  <si>
+    <t>3231290199 3231290199</t>
+  </si>
+  <si>
+    <t>3231340020 3231340020</t>
+  </si>
+  <si>
+    <t>3231335659 3231335659</t>
+  </si>
+  <si>
+    <t>3231542111 3231542111</t>
+  </si>
+  <si>
+    <t>3231589015 3231589015</t>
   </si>
   <si>
     <t>Общи литри по продукт / ИВОН СТРОЙ 2015 ЕООД</t>
@@ -512,24 +542,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -569,215 +601,233 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1199</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>75</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>124.5</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>135</v>
       </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>263386</v>
+      <c r="N2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1163</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>36.67</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>60.87</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>66.01000000000001</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>110867</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>1199</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>49.75</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
         <v>1.66</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>82.58</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.8</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>89.55</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>263664</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1911</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>48.23</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5">
         <v>1.66</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>80.06</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>86.81</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>175648</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1199</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
       </c>
       <c r="F6">
         <v>66</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6">
         <v>1.65</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>108.9</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.79</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>118.14</v>
       </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>265060</v>
+      <c r="N6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -785,29 +835,29 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B11" s="6">
         <v>275.65</v>
@@ -825,9 +875,9 @@
         <v>495.51</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12" s="8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B12" s="9">
         <v>275.65</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
@@ -172,7 +172,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,12 +182,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -237,17 +231,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,34 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1163 София Ботевградско шосе</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>Варна</t>
   </si>
   <si>
     <t>ДЛ5</t>
@@ -85,40 +67,10 @@
     <t>78970151027720559</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>07:02:00</t>
-  </si>
-  <si>
-    <t>22:38:00</t>
-  </si>
-  <si>
-    <t>09:15:00</t>
-  </si>
-  <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>07:07:00</t>
-  </si>
-  <si>
-    <t>3231290199 3231290199</t>
-  </si>
-  <si>
-    <t>3231340020 3231340020</t>
-  </si>
-  <si>
-    <t>3231335659 3231335659</t>
-  </si>
-  <si>
-    <t>3231542111 3231542111</t>
-  </si>
-  <si>
-    <t>3231589015 3231589015</t>
   </si>
   <si>
     <t>Общи литри по продукт / ИВОН СТРОЙ 2015 ЕООД</t>
@@ -536,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -545,17 +497,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -589,307 +538,238 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H2">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>15.7</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>65.53</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H3">
+        <v>104.19</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="J3">
+        <v>108.78</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J4">
+        <v>15.6</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F5">
+        <v>49.91</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H5">
+        <v>79.36</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J5">
+        <v>79.86</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F2">
-        <v>75</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="6">
+        <v>115.44</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1.59</v>
+      </c>
+      <c r="E10" s="6">
+        <v>183.55</v>
+      </c>
+      <c r="F10" s="6">
+        <v>188.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="6">
+        <v>20</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="E11" s="6">
+        <v>30</v>
+      </c>
+      <c r="F11" s="6">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H2">
-        <v>1.66</v>
-      </c>
-      <c r="I2" s="1">
-        <v>124.5</v>
-      </c>
-      <c r="J2">
-        <v>1.8</v>
-      </c>
-      <c r="K2" s="1">
-        <v>135</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>36.67</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.66</v>
-      </c>
-      <c r="I3" s="1">
-        <v>60.87</v>
-      </c>
-      <c r="J3">
-        <v>1.8</v>
-      </c>
-      <c r="K3" s="1">
-        <v>66.01000000000001</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4">
-        <v>49.75</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>1.66</v>
-      </c>
-      <c r="I4" s="1">
-        <v>82.58</v>
-      </c>
-      <c r="J4">
-        <v>1.8</v>
-      </c>
-      <c r="K4" s="1">
-        <v>89.55</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>48.23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5">
-        <v>1.66</v>
-      </c>
-      <c r="I5" s="1">
-        <v>80.06</v>
-      </c>
-      <c r="J5">
-        <v>1.8</v>
-      </c>
-      <c r="K5" s="1">
-        <v>86.81</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>66</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>1.65</v>
-      </c>
-      <c r="I6" s="1">
-        <v>108.9</v>
-      </c>
-      <c r="J6">
-        <v>1.79</v>
-      </c>
-      <c r="K6" s="1">
-        <v>118.14</v>
-      </c>
-      <c r="L6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="6">
-        <v>275.65</v>
-      </c>
-      <c r="C11" s="6">
-        <v>5</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.6576</v>
-      </c>
-      <c r="E11" s="6">
-        <v>456.91</v>
-      </c>
-      <c r="F11" s="6">
-        <v>495.51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="B12" s="9">
-        <v>275.65</v>
+        <v>135.44</v>
       </c>
       <c r="C12" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="9">
-        <v>456.91</v>
+        <v>213.55</v>
       </c>
       <c r="F12" s="9">
-        <v>495.51</v>
+        <v>219.94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-04</t>
   </si>
   <si>
@@ -61,7 +70,7 @@
     <t>2026-06-20</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>ДЛ5</t>
@@ -70,28 +79,37 @@
     <t>78970151027720559</t>
   </si>
   <si>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>2026-06-04 10:00:15</t>
-  </si>
-  <si>
-    <t>2026-06-04 10:00:16</t>
-  </si>
-  <si>
-    <t>2026-06-11 08:22:46</t>
-  </si>
-  <si>
-    <t>2026-06-13 10:17:39</t>
-  </si>
-  <si>
-    <t>2026-06-20 17:11:20</t>
-  </si>
-  <si>
-    <t>2026-06-20 17:11:21</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>08:23:00</t>
+  </si>
+  <si>
+    <t>10:18:00</t>
+  </si>
+  <si>
+    <t>17:12:00</t>
+  </si>
+  <si>
+    <t>3232859290 3232859290</t>
+  </si>
+  <si>
+    <t>3233203713 3233203713</t>
+  </si>
+  <si>
+    <t>3233289986 3233289986</t>
+  </si>
+  <si>
+    <t>3233627559 3233627559</t>
   </si>
   <si>
     <t>Общи литри по продукт / ИВОН СТРОЙ 2015 ЕООД</t>
@@ -509,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,14 +536,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,220 +580,283 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>65.53</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2">
+        <v>1.56</v>
+      </c>
+      <c r="I2" s="1">
+        <v>102.23</v>
+      </c>
+      <c r="J2">
+        <v>1.66</v>
+      </c>
+      <c r="K2" s="1">
+        <v>108.78</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3">
+        <v>1.49</v>
+      </c>
+      <c r="I3" s="1">
+        <v>14.9</v>
+      </c>
+      <c r="J3">
+        <v>1.57</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H2">
-        <v>14.9</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>15.7</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>65.53</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="H3">
-        <v>102.23</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="J3">
-        <v>108.78</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>10</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4">
         <v>1.46</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>14.6</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.56</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>15.6</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>49.91</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5">
         <v>1.53</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>76.36</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.6</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>79.86</v>
       </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>73.94</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6">
         <v>1.49</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>110.17</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>113.87</v>
       </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>10</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7">
         <v>1.42</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>14.2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.53</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>15.3</v>
       </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L7" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -780,29 +864,29 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="6">
         <v>189.38</v>
@@ -820,9 +904,9 @@
         <v>302.51</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B13" s="6">
         <v>30</v>
@@ -840,9 +924,9 @@
         <v>46.6</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:14">
       <c r="A14" s="8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B14" s="9">
         <v>219.38</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -61,13 +67,31 @@
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>София Ботевградско шосе</t>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1163 София Ботевградско шосе</t>
+  </si>
+  <si>
+    <t>1178 Русе, бул. България</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
   </si>
   <si>
     <t>ДЛ5</t>
@@ -82,19 +106,73 @@
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>2026-07-01 17:25:23</t>
-  </si>
-  <si>
-    <t>2026-07-11 15:58:41</t>
-  </si>
-  <si>
-    <t>2026-07-11 19:50:47</t>
-  </si>
-  <si>
-    <t>2026-07-14 11:57:27</t>
-  </si>
-  <si>
-    <t>2026-07-14 23:13:35</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>17:26:00</t>
+  </si>
+  <si>
+    <t>15:58:00</t>
+  </si>
+  <si>
+    <t>19:50:00</t>
+  </si>
+  <si>
+    <t>23:13:00</t>
+  </si>
+  <si>
+    <t>11:58:00</t>
+  </si>
+  <si>
+    <t>08:33:00</t>
+  </si>
+  <si>
+    <t>23:01:00</t>
+  </si>
+  <si>
+    <t>12:05:00</t>
+  </si>
+  <si>
+    <t>09:50:00</t>
+  </si>
+  <si>
+    <t>06:46:00</t>
+  </si>
+  <si>
+    <t>14:43:00</t>
+  </si>
+  <si>
+    <t>3234118657 3234118657</t>
+  </si>
+  <si>
+    <t>3234589359 3234589359</t>
+  </si>
+  <si>
+    <t>3234658809 3234658809</t>
+  </si>
+  <si>
+    <t>3234801470 3234801470</t>
+  </si>
+  <si>
+    <t>3234801338 3234801338</t>
+  </si>
+  <si>
+    <t>3235151305 3235151305</t>
+  </si>
+  <si>
+    <t>3235200886 3235200886</t>
+  </si>
+  <si>
+    <t>3235200703 3235200703</t>
+  </si>
+  <si>
+    <t>3235536095 3235536095</t>
+  </si>
+  <si>
+    <t>3235536979 3235536979</t>
+  </si>
+  <si>
+    <t>3235589436 3235589436</t>
   </si>
   <si>
     <t>Общи литри по продукт / ИВОН СТРОЙ 2015 ЕООД</t>
@@ -512,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,15 +599,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -566,288 +646,588 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>67</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2">
         <v>1.42</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>95.14</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>101.17</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>77.23999999999999</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
         <v>1.46</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>112.77</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.54</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>118.95</v>
       </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>32</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4">
         <v>1.46</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>46.72</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.54</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>49.28</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>35.47</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>1.49</v>
+      </c>
+      <c r="I5" s="1">
+        <v>52.85</v>
+      </c>
+      <c r="J5">
+        <v>1.56</v>
+      </c>
+      <c r="K5" s="1">
+        <v>55.33</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6">
+        <v>35.7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>1.82</v>
+      </c>
+      <c r="I6" s="1">
+        <v>64.97</v>
+      </c>
+      <c r="J6">
+        <v>1.82</v>
+      </c>
+      <c r="K6" s="1">
+        <v>64.97</v>
+      </c>
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>1.58</v>
+      </c>
+      <c r="I7" s="1">
+        <v>75.84</v>
+      </c>
+      <c r="J7">
+        <v>1.68</v>
+      </c>
+      <c r="K7" s="1">
+        <v>80.64</v>
+      </c>
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>34.01</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>1.61</v>
+      </c>
+      <c r="I8" s="1">
+        <v>54.76</v>
+      </c>
+      <c r="J8">
+        <v>1.7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>57.82</v>
+      </c>
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9">
+        <v>11.29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9">
+        <v>1.95</v>
+      </c>
+      <c r="I9" s="1">
+        <v>22.02</v>
+      </c>
+      <c r="J9">
+        <v>1.95</v>
+      </c>
+      <c r="K9" s="1">
+        <v>22.02</v>
+      </c>
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="L4">
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10">
+        <v>17.65</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10">
+        <v>1.69</v>
+      </c>
+      <c r="I10" s="1">
+        <v>29.83</v>
+      </c>
+      <c r="J10">
+        <v>1.75</v>
+      </c>
+      <c r="K10" s="1">
+        <v>30.89</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="N10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="F5">
-        <v>35.7</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="H5">
-        <v>64.97</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="J5">
-        <v>64.97</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11">
+        <v>35</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>1.69</v>
+      </c>
+      <c r="I11" s="1">
+        <v>59.15</v>
+      </c>
+      <c r="J11">
+        <v>1.75</v>
+      </c>
+      <c r="K11" s="1">
+        <v>61.25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="L5">
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12">
+        <v>47.31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12">
+        <v>1.69</v>
+      </c>
+      <c r="I12" s="1">
+        <v>79.95</v>
+      </c>
+      <c r="J12">
+        <v>1.76</v>
+      </c>
+      <c r="K12" s="1">
+        <v>83.27</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>35.47</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H6">
-        <v>52.85</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J6">
-        <v>55.33</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
+      <c r="N12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B17" s="6">
+        <v>393.68</v>
+      </c>
+      <c r="C17" s="6">
+        <v>9</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.5419</v>
+      </c>
+      <c r="E17" s="6">
+        <v>607.01</v>
+      </c>
+      <c r="F17" s="6">
+        <v>638.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="6">
-        <v>211.71</v>
-      </c>
-      <c r="C11" s="6">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.4524</v>
-      </c>
-      <c r="E11" s="6">
-        <v>307.48</v>
-      </c>
-      <c r="F11" s="6">
-        <v>324.73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="6">
-        <v>35.7</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.8199</v>
-      </c>
-      <c r="E12" s="6">
-        <v>64.97</v>
-      </c>
-      <c r="F12" s="6">
-        <v>64.97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="9">
-        <v>247.41</v>
-      </c>
-      <c r="C13" s="9">
-        <v>5</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9">
-        <v>372.45</v>
-      </c>
-      <c r="F13" s="9">
-        <v>389.7</v>
+      <c r="B18" s="6">
+        <v>46.99</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1.8512</v>
+      </c>
+      <c r="E18" s="6">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="F18" s="6">
+        <v>86.98999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="9">
+        <v>440.67</v>
+      </c>
+      <c r="C19" s="9">
+        <v>11</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="9">
+        <v>694</v>
+      </c>
+      <c r="F19" s="9">
+        <v>725.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
@@ -199,7 +199,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1178,7 +1178,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="7">
-        <v>1.5419</v>
+        <v>1.541887</v>
       </c>
       <c r="E17" s="6">
         <v>607.01</v>
@@ -1198,7 +1198,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="7">
-        <v>1.8512</v>
+        <v>1.851245</v>
       </c>
       <c r="E18" s="6">
         <v>86.98999999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -590,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -603,13 +606,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -652,494 +655,530 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2">
-        <v>1.42</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>95.14</v>
+        <v>1.419</v>
       </c>
       <c r="J2">
+        <v>95.07299999999999</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>101.17</v>
       </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>77.23999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3">
-        <v>1.46</v>
+        <v>1.437</v>
       </c>
       <c r="I3" s="1">
-        <v>112.77</v>
+        <v>1.457</v>
       </c>
       <c r="J3">
+        <v>112.53868</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.54</v>
       </c>
-      <c r="K3" s="1">
-        <v>118.95</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>118.9496</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>32</v>
       </c>
       <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
+        <v>1.437</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.457</v>
+      </c>
+      <c r="J4">
+        <v>46.624</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L4" s="1">
+        <v>49.28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5">
+        <v>35.468</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
+        <v>1.469</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.489</v>
+      </c>
+      <c r="J5">
+        <v>52.811852</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L5" s="1">
+        <v>55.33008</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="H4">
-        <v>1.46</v>
-      </c>
-      <c r="I4" s="1">
-        <v>46.72</v>
-      </c>
-      <c r="J4">
-        <v>1.54</v>
-      </c>
-      <c r="K4" s="1">
-        <v>49.28</v>
-      </c>
-      <c r="L4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>35.47</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5">
-        <v>1.49</v>
-      </c>
-      <c r="I5" s="1">
-        <v>52.85</v>
-      </c>
-      <c r="J5">
-        <v>1.56</v>
-      </c>
-      <c r="K5" s="1">
-        <v>55.33</v>
-      </c>
-      <c r="L5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
       <c r="F6">
-        <v>35.7</v>
+        <v>35.698</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6">
         <v>1.82</v>
       </c>
       <c r="I6" s="1">
-        <v>64.97</v>
+        <v>1.82</v>
       </c>
       <c r="J6">
+        <v>64.97036</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.82</v>
       </c>
-      <c r="K6" s="1">
-        <v>64.97</v>
-      </c>
-      <c r="L6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>64.97036</v>
+      </c>
+      <c r="M6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>48</v>
       </c>
       <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>1.564</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.584</v>
+      </c>
+      <c r="J7">
+        <v>76.032</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L7" s="1">
+        <v>80.64</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>34.012</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8">
+        <v>1.588</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.608</v>
+      </c>
+      <c r="J8">
+        <v>54.691296</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L8" s="1">
+        <v>57.8204</v>
+      </c>
+      <c r="M8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
         <v>30</v>
       </c>
-      <c r="H7">
-        <v>1.58</v>
-      </c>
-      <c r="I7" s="1">
-        <v>75.84</v>
-      </c>
-      <c r="J7">
-        <v>1.68</v>
-      </c>
-      <c r="K7" s="1">
-        <v>80.64</v>
-      </c>
-      <c r="L7" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8">
-        <v>34.01</v>
-      </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8">
-        <v>1.61</v>
-      </c>
-      <c r="I8" s="1">
-        <v>54.76</v>
-      </c>
-      <c r="J8">
-        <v>1.7</v>
-      </c>
-      <c r="K8" s="1">
-        <v>57.82</v>
-      </c>
-      <c r="L8" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
       <c r="F9">
-        <v>11.29</v>
+        <v>11.292</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9">
         <v>1.95</v>
       </c>
       <c r="I9" s="1">
-        <v>22.02</v>
+        <v>1.95</v>
       </c>
       <c r="J9">
+        <v>22.0194</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.95</v>
       </c>
-      <c r="K9" s="1">
-        <v>22.02</v>
-      </c>
-      <c r="L9" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>22.0194</v>
+      </c>
+      <c r="M9" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10">
+        <v>17.651</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10">
+        <v>1.674</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.694</v>
+      </c>
+      <c r="J10">
+        <v>29.900794</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L10" s="1">
+        <v>30.88925</v>
+      </c>
+      <c r="M10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D11" t="s">
         <v>28</v>
       </c>
-      <c r="F10">
-        <v>17.65</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10">
-        <v>1.69</v>
-      </c>
-      <c r="I10" s="1">
-        <v>29.83</v>
-      </c>
-      <c r="J10">
-        <v>1.75</v>
-      </c>
-      <c r="K10" s="1">
-        <v>30.89</v>
-      </c>
-      <c r="L10" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11">
         <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H11">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I11" s="1">
-        <v>59.15</v>
+        <v>1.694</v>
       </c>
       <c r="J11">
+        <v>59.29</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.75</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>61.25</v>
       </c>
-      <c r="L11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11">
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>47.31</v>
+        <v>47.313</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I12" s="1">
-        <v>79.95</v>
+        <v>1.694</v>
       </c>
       <c r="J12">
+        <v>80.148222</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.76</v>
       </c>
-      <c r="K12" s="1">
-        <v>83.27</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12">
+      <c r="L12" s="1">
+        <v>83.27088000000001</v>
+      </c>
+      <c r="M12" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1147,41 +1186,41 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="6">
-        <v>393.68</v>
+        <v>393.684</v>
       </c>
       <c r="C17" s="6">
         <v>9</v>
       </c>
       <c r="D17" s="7">
-        <v>1.541887</v>
+        <v>1.542125</v>
       </c>
       <c r="E17" s="6">
-        <v>607.01</v>
+        <v>607.11</v>
       </c>
       <c r="F17" s="6">
         <v>638.6</v>
@@ -1189,7 +1228,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6">
         <v>46.99</v>
@@ -1198,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="7">
-        <v>1.851245</v>
+        <v>1.85124</v>
       </c>
       <c r="E18" s="6">
         <v>86.98999999999999</v>
@@ -1209,17 +1248,17 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="9">
-        <v>440.67</v>
+        <v>440.674</v>
       </c>
       <c r="C19" s="9">
         <v>11</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="9">
-        <v>694</v>
+        <v>694.1</v>
       </c>
       <c r="F19" s="9">
         <v>725.59</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВОН СТРОЙ 2015 ЕООД/ИВОН СТРОЙ 2015 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="59">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -201,8 +198,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -295,10 +292,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -606,13 +603,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -655,530 +652,494 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
       </c>
       <c r="F2">
         <v>67</v>
       </c>
       <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2">
+        <v>1.419</v>
+      </c>
+      <c r="I2" s="1">
+        <v>95.07299999999999</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>101.17</v>
+      </c>
+      <c r="L2" t="s">
         <v>31</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.419</v>
-      </c>
-      <c r="J2">
-        <v>95.07299999999999</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>101.17</v>
-      </c>
-      <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
       </c>
       <c r="F3">
         <v>77.23999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>1.437</v>
+        <v>1.457</v>
       </c>
       <c r="I3" s="1">
-        <v>1.457</v>
+        <v>112.539</v>
       </c>
       <c r="J3">
-        <v>112.53868</v>
+        <v>1.54</v>
       </c>
       <c r="K3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L3" s="1">
-        <v>118.9496</v>
-      </c>
-      <c r="M3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3">
+        <v>118.95</v>
+      </c>
+      <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
       </c>
       <c r="F4">
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>1.437</v>
+        <v>1.457</v>
       </c>
       <c r="I4" s="1">
-        <v>1.457</v>
+        <v>46.624</v>
       </c>
       <c r="J4">
-        <v>46.624</v>
+        <v>1.54</v>
       </c>
       <c r="K4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L4" s="1">
         <v>49.28</v>
       </c>
-      <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
       </c>
       <c r="F5">
         <v>35.468</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>1.469</v>
+        <v>1.489</v>
       </c>
       <c r="I5" s="1">
-        <v>1.489</v>
+        <v>52.812</v>
       </c>
       <c r="J5">
-        <v>52.811852</v>
+        <v>1.56</v>
       </c>
       <c r="K5" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L5" s="1">
-        <v>55.33008</v>
-      </c>
-      <c r="M5" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5">
+        <v>55.33</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>35.698</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>1.82</v>
       </c>
       <c r="I6" s="1">
+        <v>64.97</v>
+      </c>
+      <c r="J6">
         <v>1.82</v>
       </c>
-      <c r="J6">
-        <v>64.97036</v>
-      </c>
       <c r="K6" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L6" s="1">
-        <v>64.97036</v>
-      </c>
-      <c r="M6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6">
+        <v>64.97</v>
+      </c>
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
       </c>
       <c r="F7">
         <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H7">
-        <v>1.564</v>
+        <v>1.584</v>
       </c>
       <c r="I7" s="1">
-        <v>1.584</v>
+        <v>76.032</v>
       </c>
       <c r="J7">
-        <v>76.032</v>
+        <v>1.68</v>
       </c>
       <c r="K7" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L7" s="1">
         <v>80.64</v>
       </c>
-      <c r="M7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7">
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
       </c>
       <c r="F8">
         <v>34.012</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I8" s="1">
-        <v>1.608</v>
+        <v>54.691</v>
       </c>
       <c r="J8">
-        <v>54.691296</v>
+        <v>1.7</v>
       </c>
       <c r="K8" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L8" s="1">
-        <v>57.8204</v>
-      </c>
-      <c r="M8" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8">
+        <v>57.82</v>
+      </c>
+      <c r="L8" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
         <v>27</v>
       </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>11.292</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H9">
         <v>1.95</v>
       </c>
       <c r="I9" s="1">
+        <v>22.019</v>
+      </c>
+      <c r="J9">
         <v>1.95</v>
       </c>
-      <c r="J9">
-        <v>22.0194</v>
-      </c>
       <c r="K9" s="1">
-        <v>1.95</v>
-      </c>
-      <c r="L9" s="1">
-        <v>22.0194</v>
-      </c>
-      <c r="M9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9">
+        <v>22.019</v>
+      </c>
+      <c r="L9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>29</v>
       </c>
       <c r="F10">
         <v>17.651</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I10" s="1">
-        <v>1.694</v>
+        <v>29.901</v>
       </c>
       <c r="J10">
-        <v>29.900794</v>
+        <v>1.75</v>
       </c>
       <c r="K10" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L10" s="1">
-        <v>30.88925</v>
-      </c>
-      <c r="M10" t="s">
-        <v>40</v>
-      </c>
-      <c r="N10">
+        <v>30.889</v>
+      </c>
+      <c r="L10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
       </c>
       <c r="F11">
         <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H11">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I11" s="1">
-        <v>1.694</v>
+        <v>59.29</v>
       </c>
       <c r="J11">
-        <v>59.29</v>
+        <v>1.75</v>
       </c>
       <c r="K11" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L11" s="1">
         <v>61.25</v>
       </c>
-      <c r="M11" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11">
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>29</v>
       </c>
       <c r="F12">
         <v>47.313</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H12">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I12" s="1">
-        <v>1.694</v>
+        <v>80.148</v>
       </c>
       <c r="J12">
-        <v>80.148222</v>
+        <v>1.76</v>
       </c>
       <c r="K12" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L12" s="1">
-        <v>83.27088000000001</v>
-      </c>
-      <c r="M12" t="s">
-        <v>42</v>
-      </c>
-      <c r="N12">
+        <v>83.271</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
+      <c r="N12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1186,69 +1147,69 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>58</v>
-      </c>
       <c r="E16" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="6">
         <v>393.684</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>9</v>
       </c>
       <c r="D17" s="7">
-        <v>1.542125</v>
-      </c>
-      <c r="E17" s="6">
+        <v>1.542</v>
+      </c>
+      <c r="E17" s="7">
         <v>607.11</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <v>638.6</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="6">
         <v>46.99</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <v>2</v>
       </c>
       <c r="D18" s="7">
-        <v>1.85124</v>
-      </c>
-      <c r="E18" s="6">
-        <v>86.98999999999999</v>
-      </c>
-      <c r="F18" s="6">
-        <v>86.98999999999999</v>
+        <v>1.851</v>
+      </c>
+      <c r="E18" s="7">
+        <v>86.989</v>
+      </c>
+      <c r="F18" s="7">
+        <v>86.989</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="9">
         <v>440.674</v>
@@ -1258,10 +1219,10 @@
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="9">
-        <v>694.1</v>
+        <v>694.099</v>
       </c>
       <c r="F19" s="9">
-        <v>725.59</v>
+        <v>725.5890000000001</v>
       </c>
     </row>
   </sheetData>
